--- a/course-design-2/outputs/tables/ch4/36_stage26_1_episode_rebuild_audit.xlsx
+++ b/course-design-2/outputs/tables/ch4/36_stage26_1_episode_rebuild_audit.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_T3合并前后对照" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_异常时间记录" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_人工抽查" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_口径说明" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_统计范围说明" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_转换间隔分布" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_人工抽样说明" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_规模对照" sheetId="11" state="visible" r:id="rId11"/>

--- a/course-design-2/outputs/tables/ch4/36_stage26_1_episode_rebuild_audit.xlsx
+++ b/course-design-2/outputs/tables/ch4/36_stage26_1_episode_rebuild_audit.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Stage26 旧口径（复核实测）</t>
+          <t>Stage26 旧统计范围（复核实测）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Stage26 旧口径（复核实测）</t>
+          <t>Stage26 旧统计范围（复核实测）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -14229,9 +14229,6 @@
           <t>NaT</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="n">
         <v>0</v>
       </c>
@@ -16154,8 +16151,6 @@
           <t>发布日晚于上一周期结束日且间隔 ≥ 7 天，符合重新招聘定义；仍需人工确认是否同一岗位真实重招</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -16205,8 +16200,6 @@
           <t>发布日晚于上一周期结束日且间隔 ≥ 7 天，符合重新招聘定义；仍需人工确认是否同一岗位真实重招</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16256,8 +16249,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -16307,8 +16298,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -16358,8 +16347,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -16409,8 +16396,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -16460,8 +16445,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -16511,8 +16494,6 @@
           <t>与上一周期结束日间隔 0 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -16562,8 +16543,6 @@
           <t>与上一周期结束日间隔 0 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -16613,8 +16592,6 @@
           <t>与上一周期结束日间隔 0 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -16664,8 +16641,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -16715,8 +16690,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -16766,8 +16739,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -16817,8 +16788,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -16868,8 +16837,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -16919,8 +16886,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16970,8 +16935,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17021,8 +16984,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17072,8 +17033,6 @@
           <t>与上一周期结束日间隔 2 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17123,8 +17082,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17174,8 +17131,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -17225,8 +17180,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -17276,8 +17229,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -17327,8 +17278,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17378,8 +17327,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -17429,8 +17376,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -17480,8 +17425,6 @@
           <t>与上一周期结束日间隔 1 日历天（&lt; 7 天），疑平台发布时间 / 截止日期被重置，严格口径归并</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -17531,8 +17474,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -17582,8 +17523,6 @@
           <t>本次发布时间早于上一周期结束日 1 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -17633,8 +17572,6 @@
           <t>本次发布时间早于上一周期结束日 5 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -17684,8 +17621,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17735,8 +17670,6 @@
           <t>本次发布时间早于上一周期结束日 278 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -17786,8 +17719,6 @@
           <t>本次发布时间早于上一周期结束日 19 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -17837,8 +17768,6 @@
           <t>本次发布时间早于上一周期结束日 17 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -17888,8 +17817,6 @@
           <t>本次发布时间早于上一周期结束日 19 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -17939,8 +17866,6 @@
           <t>本次发布时间早于上一周期结束日 16 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -17990,8 +17915,6 @@
           <t>本次发布时间早于上一周期结束日 222 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -18041,8 +17964,6 @@
           <t>本次发布时间早于上一周期结束日 9 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -18092,8 +18013,6 @@
           <t>本次发布时间早于上一周期结束日 8 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -18143,8 +18062,6 @@
           <t>本次发布时间早于上一周期结束日 5 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -18194,8 +18111,6 @@
           <t>本次发布时间早于上一周期结束日 338 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -18245,8 +18160,6 @@
           <t>本次发布时间早于上一周期结束日 34 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -18296,8 +18209,6 @@
           <t>本次发布时间早于上一周期结束日 28 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -18347,8 +18258,6 @@
           <t>本次发布时间早于上一周期结束日 26 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -18398,8 +18307,6 @@
           <t>本次发布时间早于上一周期结束日 30 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -18449,8 +18356,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -18500,8 +18405,6 @@
           <t>本次发布时间早于上一周期结束日 5 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -18551,8 +18454,6 @@
           <t>本次发布时间早于上一周期结束日 242 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -18602,8 +18503,6 @@
           <t>本次发布时间早于上一周期结束日 171 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -18653,8 +18552,6 @@
           <t>本次发布时间早于上一周期结束日 170 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -18704,8 +18601,6 @@
           <t>本次发布时间早于上一周期结束日 1 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -18755,8 +18650,6 @@
           <t>本次发布时间早于上一周期结束日 12 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -18806,8 +18699,6 @@
           <t>本次发布时间早于上一周期结束日 339 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -18857,8 +18748,6 @@
           <t>本次发布时间早于上一周期结束日 332 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -18908,8 +18797,6 @@
           <t>本次发布时间早于上一周期结束日 329 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -18959,8 +18846,6 @@
           <t>本次发布时间早于上一周期结束日 19 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -19010,8 +18895,6 @@
           <t>本次发布时间早于上一周期结束日 17 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -19061,8 +18944,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -19112,8 +18993,6 @@
           <t>本次发布时间早于上一周期结束日 282 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -19163,8 +19042,6 @@
           <t>本次发布时间早于上一周期结束日 8 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -19214,8 +19091,6 @@
           <t>本次发布时间早于上一周期结束日 6 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -19265,8 +19140,6 @@
           <t>本次发布时间早于上一周期结束日 4 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -19316,8 +19189,6 @@
           <t>本次发布时间早于上一周期结束日 1 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -19367,8 +19238,6 @@
           <t>本次发布时间早于上一周期结束日 197 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -19418,8 +19287,6 @@
           <t>本次发布时间早于上一周期结束日 347 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -19469,8 +19336,6 @@
           <t>本次发布时间早于上一周期结束日 14 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -19520,8 +19385,6 @@
           <t>本次发布时间早于上一周期结束日 289 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -19571,8 +19434,6 @@
           <t>本次发布时间早于上一周期结束日 279 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -19622,8 +19483,6 @@
           <t>本次发布时间早于上一周期结束日 4 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -19673,8 +19532,6 @@
           <t>本次发布时间早于上一周期结束日 12 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -19724,8 +19581,6 @@
           <t>本次发布时间早于上一周期结束日 222 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -19775,8 +19630,6 @@
           <t>本次发布时间早于上一周期结束日 6 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -19826,8 +19679,6 @@
           <t>本次发布时间早于上一周期结束日 229 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -19877,8 +19728,6 @@
           <t>本次发布时间早于上一周期结束日 289 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -19928,8 +19777,6 @@
           <t>本次发布时间早于上一周期结束日 284 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -19979,8 +19826,6 @@
           <t>本次发布时间早于上一周期结束日 10 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -20030,8 +19875,6 @@
           <t>本次发布时间早于上一周期结束日 298 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -20081,8 +19924,6 @@
           <t>本次发布时间早于上一周期结束日 3 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -20132,8 +19973,6 @@
           <t>本次发布时间早于上一周期结束日 199 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -20183,8 +20022,6 @@
           <t>本次发布时间早于上一周期结束日 198 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -20234,8 +20071,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -20285,8 +20120,6 @@
           <t>本次发布时间早于上一周期结束日 16 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -20336,8 +20169,6 @@
           <t>本次发布时间早于上一周期结束日 15 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -20387,8 +20218,6 @@
           <t>本次发布时间早于上一周期结束日 14 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -20438,8 +20267,6 @@
           <t>本次发布时间早于上一周期结束日 68 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -20489,8 +20316,6 @@
           <t>本次发布时间早于上一周期结束日 7 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -20540,8 +20365,6 @@
           <t>本次发布时间早于上一周期结束日 282 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -20591,8 +20414,6 @@
           <t>本次发布时间早于上一周期结束日 281 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -20642,8 +20463,6 @@
           <t>本次发布时间早于上一周期结束日 6 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -20693,8 +20512,6 @@
           <t>本次发布时间早于上一周期结束日 1 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -20744,8 +20561,6 @@
           <t>本次发布时间早于上一周期结束日 275 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -20795,8 +20610,6 @@
           <t>本次发布时间早于上一周期结束日 9 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -20846,8 +20659,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -20897,8 +20708,6 @@
           <t>本次发布时间早于上一周期结束日 16 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -20948,8 +20757,6 @@
           <t>本次发布时间早于上一周期结束日 10 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -20999,8 +20806,6 @@
           <t>本次发布时间早于上一周期结束日 9 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -21050,8 +20855,6 @@
           <t>本次发布时间早于上一周期结束日 26 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -21101,8 +20904,6 @@
           <t>本次发布时间早于上一周期结束日 16 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -21152,8 +20953,6 @@
           <t>本次发布时间早于上一周期结束日 9 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -21203,8 +21002,6 @@
           <t>本次发布时间早于上一周期结束日 16 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -21254,8 +21051,6 @@
           <t>本次发布时间早于上一周期结束日 10 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -21305,8 +21100,6 @@
           <t>本次发布时间早于上一周期结束日 9 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -21356,8 +21149,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -21407,8 +21198,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -21458,8 +21247,6 @@
           <t>本次发布时间早于上一周期结束日 194 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -21509,8 +21296,6 @@
           <t>本次发布时间早于上一周期结束日 275 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -21560,8 +21345,6 @@
           <t>本次发布时间早于上一周期结束日 274 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -21611,8 +21394,6 @@
           <t>本次发布时间早于上一周期结束日 7 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -21662,8 +21443,6 @@
           <t>本次发布时间早于上一周期结束日 85 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -21713,8 +21492,6 @@
           <t>本次发布时间早于上一周期结束日 12 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -21764,8 +21541,6 @@
           <t>本次发布时间早于上一周期结束日 279 日历天，按规则不判重招，保守处理为时间冲突并归并</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21824,10 +21599,6 @@
           <t>全页面版本：同一岗位内连续相同完整页面签名的观测快照压缩为 1 个版本</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21840,10 +21611,6 @@
           <t>同一岗位内按观测时间排序后，连续相同「发布时间」的全页面版本归入同一段；同一发布时间内的截止日期 / 薪资 / 描述变化只形成 Version，不形成新 Segment</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21856,10 +21623,6 @@
           <t>T1 新建；T2 / T3 归并（严格主口径）</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21872,10 +21635,6 @@
           <t>T1 + T2 新建；T3 归并（敏感性口径）</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21888,10 +21647,6 @@
           <t>start &gt; 当前 Episode 结束日且 gap ≥ 7 天</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21904,10 +21659,6 @@
           <t>start &gt; 当前 Episode 结束日且 0 &lt; gap &lt; 7 天</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21920,10 +21671,6 @@
           <t>start ≤ 当前 Episode 结束日</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21936,10 +21683,6 @@
           <t>该 Segment 在本数据中**首次被观测**时看到的投递截止日期</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21952,10 +21695,6 @@
           <t>该 Segment **最后一次观测**时看到的投递截止日期（Epstride 级取末段值）</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21968,10 +21707,6 @@
           <t>计划持续天数 = (截止日 − 发布时间).normalize() 的日历差 + 1（含端点）；Stage26 使用 timedelta.days 截断口径，故本轮长度整体 +1 天</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21984,10 +21719,6 @@
           <t>因采集并非从岗位真实发布日连续观察，`initial_observed_deadline` 只是「该 Candidate Segment 在本数据中首次被观测时看到的投递截止日期」，**不等于**真实发布时的初始截止日期；对 2025 年及更早发布的岗位，研究者并未在其真实发布时持续观察页面，因此 2026 年集中采集回溯得到的版本历史不能写成「岗位发布时已观测到的信息」。</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22000,10 +21731,6 @@
           <t>T2（疑似重开，0 &lt; gap &lt; 7 天）高度集中于 1 天，极可能是平台发布时间 / 投递截止日期被重置造成的伪影，只作为敏感性 / 对照口径，不得表述为真实重新招聘，也不得据此估计总体重招率。</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22016,14 +21743,8 @@
           <t>T3（时间冲突，start ≤ 当前 Episode 结束日）不做重新招聘解释、不生成独立正式 Episode、不进入主日级面板的重复周期计数，仅保留审计记录与人工抽查样例。</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
@@ -22044,8 +21765,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2</v>
       </c>
@@ -22066,8 +21785,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>3</v>
       </c>
@@ -22088,8 +21805,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>4</v>
       </c>
@@ -22110,8 +21825,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>5</v>
       </c>
@@ -22132,8 +21845,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>6</v>
       </c>
@@ -22154,8 +21865,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>7</v>
       </c>
@@ -22176,8 +21885,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>8</v>
       </c>
@@ -22198,8 +21905,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>9</v>
       </c>
@@ -22220,8 +21925,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>10</v>
       </c>
@@ -22289,7 +21992,6 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22303,7 +22005,6 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22317,7 +22018,6 @@
       <c r="C4" t="n">
         <v>28</v>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22331,7 +22031,6 @@
       <c r="C5" t="n">
         <v>446</v>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22345,7 +22044,6 @@
       <c r="C6" t="n">
         <v>37</v>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22359,7 +22057,6 @@
       <c r="C7" t="n">
         <v>14</v>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22373,7 +22070,6 @@
       <c r="C8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22387,7 +22083,6 @@
       <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22401,7 +22096,6 @@
       <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22409,7 +22103,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>1</v>
       </c>
@@ -22423,7 +22116,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>1</v>
       </c>
@@ -22437,7 +22129,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>1</v>
       </c>
@@ -22451,7 +22142,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>1</v>
       </c>
@@ -22465,7 +22155,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
@@ -22479,7 +22168,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>1</v>
       </c>
@@ -22493,7 +22181,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>1</v>
       </c>
@@ -22507,7 +22194,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>1</v>
       </c>
@@ -22521,7 +22207,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>1</v>
       </c>
@@ -22535,7 +22220,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>1</v>
       </c>
@@ -22549,7 +22233,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>1</v>
       </c>
@@ -22563,7 +22246,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>1</v>
       </c>
@@ -22577,7 +22259,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>1</v>
       </c>
@@ -22591,7 +22272,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>1</v>
       </c>
@@ -22605,7 +22285,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>1</v>
       </c>
@@ -22619,7 +22298,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>1</v>
       </c>
@@ -22633,7 +22311,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>1</v>
       </c>
@@ -22647,7 +22324,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>1</v>
       </c>
@@ -22661,7 +22337,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>1</v>
       </c>
@@ -22675,7 +22350,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>1</v>
       </c>
@@ -22689,7 +22363,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>1</v>
       </c>
@@ -22703,7 +22376,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>1</v>
       </c>
@@ -22717,7 +22389,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>1</v>
       </c>
@@ -22731,7 +22402,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>1</v>
       </c>
@@ -22745,7 +22415,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>1</v>
       </c>
@@ -22759,7 +22428,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>1</v>
       </c>
@@ -22773,7 +22441,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>1</v>
       </c>
@@ -22787,7 +22454,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>1</v>
       </c>
@@ -22801,7 +22467,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>137</v>
       </c>
@@ -22815,7 +22480,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>254</v>
       </c>
@@ -22829,7 +22493,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>1</v>
       </c>
@@ -22843,7 +22506,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>1</v>
       </c>
@@ -22857,7 +22519,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>1</v>
       </c>
@@ -22871,7 +22532,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>1</v>
       </c>
@@ -22885,7 +22545,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>1</v>
       </c>
@@ -22899,7 +22558,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>1</v>
       </c>
@@ -22913,7 +22571,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>1</v>
       </c>
@@ -22927,7 +22584,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>1</v>
       </c>
@@ -22941,7 +22597,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>1</v>
       </c>
@@ -22955,7 +22610,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>1</v>
       </c>
@@ -22969,7 +22623,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>1</v>
       </c>
@@ -22983,7 +22636,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>1</v>
       </c>
@@ -22997,7 +22649,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>1</v>
       </c>
@@ -23011,7 +22662,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>1</v>
       </c>
@@ -23025,7 +22675,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>1</v>
       </c>
@@ -23039,7 +22688,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>1</v>
       </c>
@@ -23053,7 +22701,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>1</v>
       </c>
@@ -23067,7 +22714,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>1</v>
       </c>
@@ -23081,7 +22727,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>2</v>
       </c>
@@ -23095,7 +22740,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>1</v>
       </c>
@@ -23109,7 +22753,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>1</v>
       </c>
@@ -23123,7 +22766,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>1</v>
       </c>
@@ -23137,7 +22779,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>1</v>
       </c>
@@ -23151,7 +22792,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>1</v>
       </c>
@@ -23165,7 +22805,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>1</v>
       </c>
@@ -23179,7 +22818,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>1</v>
       </c>
@@ -23193,7 +22831,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>1</v>
       </c>
@@ -23207,7 +22844,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>1</v>
       </c>
@@ -23221,7 +22857,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>1</v>
       </c>
@@ -23235,7 +22870,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>1</v>
       </c>
@@ -23249,7 +22883,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>1</v>
       </c>
@@ -23263,7 +22896,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>1</v>
       </c>
@@ -23277,7 +22909,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>1</v>
       </c>
@@ -23291,7 +22922,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>1</v>
       </c>
@@ -23305,7 +22935,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>1</v>
       </c>
@@ -23319,7 +22948,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>1</v>
       </c>
@@ -23333,7 +22961,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>1</v>
       </c>
@@ -23347,7 +22974,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>1</v>
       </c>
@@ -23361,7 +22987,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>1</v>
       </c>
@@ -23375,7 +23000,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>1</v>
       </c>
@@ -23389,7 +23013,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>1</v>
       </c>
@@ -23403,7 +23026,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>1</v>
       </c>
@@ -23417,7 +23039,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>1</v>
       </c>
@@ -23431,7 +23052,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>1</v>
       </c>
@@ -23445,7 +23065,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>1</v>
       </c>
@@ -23459,7 +23078,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>1</v>
       </c>
@@ -23473,7 +23091,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>1</v>
       </c>
@@ -23487,7 +23104,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>1</v>
       </c>
@@ -23501,7 +23117,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>1</v>
       </c>
@@ -23515,7 +23130,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>1</v>
       </c>
@@ -23529,7 +23143,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>1</v>
       </c>
@@ -23543,7 +23156,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>1</v>
       </c>
@@ -23557,7 +23169,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>1</v>
       </c>
@@ -23571,7 +23182,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>1</v>
       </c>
@@ -23585,7 +23195,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>1</v>
       </c>
@@ -23599,7 +23208,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>1</v>
       </c>
@@ -23613,7 +23221,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>1</v>
       </c>
@@ -23627,7 +23234,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>1</v>
       </c>
@@ -23641,7 +23247,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>1</v>
       </c>
@@ -23655,7 +23260,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>1</v>
       </c>
@@ -23669,7 +23273,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>1</v>
       </c>
@@ -23683,7 +23286,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>1</v>
       </c>
@@ -23697,7 +23299,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>1</v>
       </c>
@@ -23711,7 +23312,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>1</v>
       </c>
@@ -23725,7 +23325,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>1</v>
       </c>
@@ -23739,7 +23338,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>1</v>
       </c>
@@ -23753,7 +23351,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>1</v>
       </c>
@@ -23767,7 +23364,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>1</v>
       </c>
@@ -23781,7 +23377,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>1</v>
       </c>
@@ -23795,7 +23390,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>1</v>
       </c>
@@ -23809,7 +23403,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>1</v>
       </c>
@@ -23823,7 +23416,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
         <v>1</v>
       </c>
@@ -23837,7 +23429,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>1</v>
       </c>
@@ -23851,7 +23442,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>1</v>
       </c>
@@ -23865,7 +23455,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>1</v>
       </c>
@@ -23879,7 +23468,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>1</v>
       </c>
@@ -23893,7 +23481,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>1</v>
       </c>
@@ -23907,7 +23494,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
         <v>1</v>
       </c>
@@ -23921,7 +23507,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>1</v>
       </c>
@@ -23935,7 +23520,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>1</v>
       </c>
@@ -23949,7 +23533,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>1</v>
       </c>
@@ -23963,7 +23546,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>1</v>
       </c>
@@ -23977,7 +23559,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>1</v>
       </c>
@@ -23991,7 +23572,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>1</v>
       </c>
@@ -24005,7 +23585,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>1</v>
       </c>
@@ -24019,7 +23598,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>1</v>
       </c>
@@ -24033,7 +23611,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>1</v>
       </c>
@@ -24047,7 +23624,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>1</v>
       </c>
@@ -24061,7 +23637,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>1</v>
       </c>
@@ -24075,7 +23650,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>1</v>
       </c>
@@ -24089,7 +23663,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>1</v>
       </c>
@@ -24103,7 +23676,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>1</v>
       </c>
@@ -24117,7 +23689,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>1</v>
       </c>
@@ -24131,7 +23702,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>1</v>
       </c>
@@ -24145,7 +23715,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>1</v>
       </c>
@@ -24159,7 +23728,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>1</v>
       </c>
@@ -24173,7 +23741,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>1</v>
       </c>
@@ -24187,7 +23754,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>1</v>
       </c>
@@ -24201,7 +23767,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>1</v>
       </c>
@@ -24215,7 +23780,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>1</v>
       </c>
@@ -24229,7 +23793,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>1</v>
       </c>
@@ -24243,7 +23806,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>1</v>
       </c>
@@ -24257,7 +23819,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>1</v>
       </c>
@@ -24271,7 +23832,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>1</v>
       </c>
@@ -24285,7 +23845,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>1</v>
       </c>
@@ -24299,7 +23858,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>1</v>
       </c>
@@ -24313,7 +23871,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>1</v>
       </c>
@@ -24327,7 +23884,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>1</v>
       </c>
@@ -24341,7 +23897,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>1</v>
       </c>
@@ -24355,7 +23910,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>1</v>
       </c>
@@ -24369,7 +23923,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>1</v>
       </c>
@@ -24383,7 +23936,6 @@
           <t>T2_SUSPECTED</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>1</v>
       </c>
